--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-14 00:30 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-15 00:59 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-16 00:51 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-17 00:55 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-17 00:55 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-18 00:49 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-22 01:15 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-23 00:58 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>2016</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-25 00:56 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-26 00:57 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
         <v>2021</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-27 00:57 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-28 01:14 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
         <v>2022</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-03 01:29 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-04 02:01 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>2030</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-06 02:32 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-07 01:51 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>2032</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-08 02:18 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-09 02:36 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>2033</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-11 01:20 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-12 01:50 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>2035</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-12 01:50 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-13 03:13 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-14 01:26 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-15 00:58 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>2036</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-17 00:49 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-18 00:27 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>2040</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-22 00:58 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-23 01:01 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>2045</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-24 01:12 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-25 00:35 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>2047</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-27 01:38 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-10-28 01:49 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>2050</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
